--- a/public/uploads/file/批量采购demo.xlsx
+++ b/public/uploads/file/批量采购demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>商品名称</t>
   </si>
@@ -58,36 +58,6 @@
   <si>
     <t>渠道用户标识ID</t>
   </si>
-  <si>
-    <t>绣榆枝休闲裤</t>
-  </si>
-  <si>
-    <t>965344644868407308</t>
-  </si>
-  <si>
-    <t>黑色直筒-常规款/M</t>
-  </si>
-  <si>
-    <t>965344644868407309</t>
-  </si>
-  <si>
-    <t>赵星宇</t>
-  </si>
-  <si>
-    <t>北京市西城区复兴门南大街丙2号天银大厦C西三层华能华北分公司党建部</t>
-  </si>
-  <si>
-    <t>水星家纺100%蚕丝被秋丰白玉蚕丝被</t>
-  </si>
-  <si>
-    <t>965344679228653568</t>
-  </si>
-  <si>
-    <t>尺寸:220cm×240cm;颜色分类:军绿色</t>
-  </si>
-  <si>
-    <t>965344679228653569</t>
-  </si>
 </sst>
 </file>
 
@@ -99,7 +69,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,24 +91,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF4A4A4A"/>
-      <name val="PingFangSC-Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF474A52"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -632,137 +584,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -780,27 +732,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1327,19 +1258,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28.75" customWidth="1"/>
-    <col min="2" max="2" width="24.375" customWidth="1"/>
-    <col min="3" max="3" width="30.625" customWidth="1"/>
-    <col min="4" max="4" width="19.375" customWidth="1"/>
-    <col min="5" max="5" width="17.375" customWidth="1"/>
-    <col min="6" max="6" width="15.375" customWidth="1"/>
-    <col min="7" max="7" width="13.75" customWidth="1"/>
-    <col min="8" max="8" width="15.375" customWidth="1"/>
-    <col min="9" max="9" width="57.875" customWidth="1"/>
-    <col min="10" max="10" width="16.25" customWidth="1"/>
+    <col min="1" max="1" width="28.7545454545455" customWidth="1"/>
+    <col min="2" max="2" width="24.3727272727273" customWidth="1"/>
+    <col min="3" max="3" width="30.6272727272727" customWidth="1"/>
+    <col min="4" max="4" width="19.3727272727273" customWidth="1"/>
+    <col min="5" max="5" width="17.3727272727273" customWidth="1"/>
+    <col min="6" max="6" width="15.3727272727273" customWidth="1"/>
+    <col min="7" max="7" width="13.7545454545455" customWidth="1"/>
+    <col min="8" max="8" width="15.3727272727273" customWidth="1"/>
+    <col min="9" max="9" width="57.8727272727273" customWidth="1"/>
+    <col min="10" max="10" width="16.2545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:10">
@@ -1374,70 +1305,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="29" customHeight="1" spans="1:10">
-      <c r="A2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="6">
-        <v>2100005215</v>
-      </c>
-      <c r="F2" s="6">
-        <v>30</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="8">
-        <v>15122089183</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="6">
-        <v>20251101</v>
-      </c>
-    </row>
-    <row r="3" ht="27" customHeight="1" spans="1:10">
-      <c r="A3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="6">
-        <v>2100005215</v>
-      </c>
-      <c r="F3" s="6">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="8">
-        <v>15122089183</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="6">
-        <v>20251101</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/uploads/file/批量采购demo.xlsx
+++ b/public/uploads/file/批量采购demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1258,19 +1258,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="28.7545454545455" customWidth="1"/>
-    <col min="2" max="2" width="24.3727272727273" customWidth="1"/>
-    <col min="3" max="3" width="30.6272727272727" customWidth="1"/>
-    <col min="4" max="4" width="19.3727272727273" customWidth="1"/>
-    <col min="5" max="5" width="17.3727272727273" customWidth="1"/>
-    <col min="6" max="6" width="15.3727272727273" customWidth="1"/>
-    <col min="7" max="7" width="13.7545454545455" customWidth="1"/>
-    <col min="8" max="8" width="15.3727272727273" customWidth="1"/>
-    <col min="9" max="9" width="57.8727272727273" customWidth="1"/>
-    <col min="10" max="10" width="16.2545454545455" customWidth="1"/>
+    <col min="1" max="1" width="28.75" customWidth="1"/>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="3" max="3" width="30.625" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="17.375" customWidth="1"/>
+    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="57.875" customWidth="1"/>
+    <col min="10" max="10" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:10">
@@ -1305,6 +1305,7 @@
         <v>9</v>
       </c>
     </row>
+    <row r="24" ht="14" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
